--- a/docs/툴팁_목록.xlsx
+++ b/docs/툴팁_목록.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1637,156 +1637,74 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>시작 설정</t>
+          <t>시작 지역 고르기(지도)</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>[모두 무작위 지도자]</t>
+          <t>지역에 커서</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>기존 규칙대로 남은 지도자 가운데 무작위로 정합니다</t>
+          <t>{지역 이름}
+(AI가 고른 곳이면) {누구}의 시작 지역</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr"/>
       <c r="F43" s="3" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>modals.py 시작 설정</t>
+          <t>app.py 시작 지역 고르기</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>시작 설정</t>
+          <t>AI 시작 지역 고르기</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>[모두 무작위 지역]</t>
+          <t>목록 칸</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>기존 규칙(수도끼리 6칸 이상 등)대로 시작 지역을 정합니다.
-내 시작 지역을 골랐으면 거기에 맞춰서</t>
+          <t>{지역 이름} / 무작위 지역</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr"/>
       <c r="F44" s="3" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>modals.py 시작 설정</t>
+          <t>app.py AI 시작 지역 고르기</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>시작 설정</t>
+          <t>지도자 고르기 창</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>[지도에서 고르기]</t>
+          <t>지도자 칸</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>지도에서 적 국가마다 시작 지역을 고릅니다</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr"/>
-      <c r="F45" s="3" t="inlineStr"/>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>modals.py 시작 설정</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>시작 지역 고르기(지도)</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>지역에 커서</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>{지역 이름}
-(AI가 고른 곳이면) {누구}의 시작 지역</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr"/>
-      <c r="F46" s="3" t="inlineStr"/>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>app.py 시작 지역 고르기</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>AI 시작 지역 고르기</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>목록 칸</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>{지역 이름} / 무작위 지역</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr"/>
-      <c r="F47" s="3" t="inlineStr"/>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>app.py AI 시작 지역 고르기</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>지도자 고르기 창</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>지도자 칸</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>(내 지도자/이미 고른 지도자면) 내 지도자입니다. / 다른 AI가 이미 골랐습니다.
 {지도자 이름}
@@ -1794,90 +1712,90 @@
 디버프 {이름}: {효과}</t>
         </is>
       </c>
+      <c r="E45" s="3" t="inlineStr"/>
+      <c r="F45" s="3" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>modals.py 지도자 고르기</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>지도자 고르기 창</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>[무작위] 칸</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>게임을 시작할 때 남은 지도자 가운데 무작위로 정합니다</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr"/>
+      <c r="F46" s="3" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>modals.py 지도자 고르기</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>국기 만들기 창</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>역사 국기·배경·문양 칸</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>{국기·배경·문양 이름}</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr"/>
+      <c r="F47" s="3" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>modals.py 국기 만들기</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>'…'로 잘린 글자</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>{잘리기 전 전체 문구}</t>
+        </is>
+      </c>
       <c r="E48" s="3" t="inlineStr"/>
       <c r="F48" s="3" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>modals.py 지도자 고르기</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>지도자 고르기 창</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>[무작위] 칸</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>게임을 시작할 때 남은 지도자 가운데 무작위로 정합니다</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr"/>
-      <c r="F49" s="3" t="inlineStr"/>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>modals.py 지도자 고르기</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>국기 만들기 창</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>역사 국기·배경·문양 칸</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>{국기·배경·문양 이름}</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr"/>
-      <c r="F50" s="3" t="inlineStr"/>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>modals.py 국기 만들기</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>'…'로 잘린 글자</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>{잘리기 전 전체 문구}</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr"/>
-      <c r="F51" s="3" t="inlineStr"/>
-      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>gui.py (모든 잘린 글자)</t>
         </is>
